--- a/data/trans_dic/IP17-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,59; 34,35</t>
+          <t>16,18; 34,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,53; 34,82</t>
+          <t>15,95; 34,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 37,19</t>
+          <t>19,7; 37,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 24,84</t>
+          <t>10,15; 24,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 34,49</t>
+          <t>16,48; 34,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,9; 40,91</t>
+          <t>20,07; 39,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,45; 38,11</t>
+          <t>19,46; 37,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 26,81</t>
+          <t>11,08; 26,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,87; 31,28</t>
+          <t>18,29; 31,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,63; 34,72</t>
+          <t>20,45; 33,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,39; 34,38</t>
+          <t>21,71; 34,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,5; 23,31</t>
+          <t>12,02; 22,91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 17,8</t>
+          <t>7,47; 18,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,76; 33,85</t>
+          <t>19,95; 33,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,85; 33,99</t>
+          <t>20,3; 35,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 16,54</t>
+          <t>5,16; 17,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 23,74</t>
+          <t>12,27; 23,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,74; 33,43</t>
+          <t>20,14; 34,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 32,77</t>
+          <t>19,24; 33,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 18,44</t>
+          <t>8,38; 19,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,2</t>
+          <t>11,32; 19,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 31,6</t>
+          <t>21,75; 31,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,04; 31,83</t>
+          <t>21,57; 31,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 16,66</t>
+          <t>7,73; 16,21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,35; 32,51</t>
+          <t>15,03; 32,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,97; 39,07</t>
+          <t>21,66; 39,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,89</t>
+          <t>7,58; 22,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 32,92</t>
+          <t>15,69; 32,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 35,51</t>
+          <t>19,55; 35,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,06; 38,3</t>
+          <t>19,59; 38,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,9; 20,98</t>
+          <t>7,67; 20,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 33,88</t>
+          <t>17,05; 34,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,43; 31,23</t>
+          <t>18,9; 30,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,67; 35,71</t>
+          <t>22,55; 35,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 18,87</t>
+          <t>8,92; 17,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 29,97</t>
+          <t>18,66; 30,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,95; 34,54</t>
+          <t>18,22; 34,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 33,71</t>
+          <t>16,6; 33,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,52; 39,58</t>
+          <t>21,44; 39,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 30,05</t>
+          <t>11,18; 28,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,31; 33,01</t>
+          <t>17,3; 33,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,88; 28,7</t>
+          <t>13,33; 28,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,74; 40,0</t>
+          <t>22,21; 40,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 31,98</t>
+          <t>9,38; 31,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 31,12</t>
+          <t>19,85; 31,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 28,52</t>
+          <t>17,69; 27,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,21; 36,61</t>
+          <t>24,65; 36,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,89; 26,14</t>
+          <t>12,3; 26,73</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,68; 29,05</t>
+          <t>9,46; 29,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,94; 39,86</t>
+          <t>15,93; 41,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 35,77</t>
+          <t>14,06; 34,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,1; 21,94</t>
+          <t>4,78; 20,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 23,31</t>
+          <t>6,29; 23,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,83; 37,05</t>
+          <t>14,71; 34,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 32,73</t>
+          <t>13,41; 33,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 23,3</t>
+          <t>6,76; 23,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 23,27</t>
+          <t>9,7; 22,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,75; 35,11</t>
+          <t>18,34; 34,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,8; 30,73</t>
+          <t>16,38; 31,07</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 19,26</t>
+          <t>7,37; 18,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,34; 30,18</t>
+          <t>12,75; 30,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,11; 40,64</t>
+          <t>19,23; 39,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,31; 32,3</t>
+          <t>14,3; 32,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,26; 28,75</t>
+          <t>11,6; 28,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,75; 25,0</t>
+          <t>9,63; 24,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 35,89</t>
+          <t>17,13; 36,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 29,66</t>
+          <t>10,67; 28,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,74; 41,79</t>
+          <t>21,1; 40,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,14; 24,81</t>
+          <t>13,11; 24,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,7; 34,76</t>
+          <t>20,31; 34,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,45; 27,23</t>
+          <t>14,35; 27,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,17; 33,08</t>
+          <t>19,48; 32,91</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,97; 32,44</t>
+          <t>19,62; 32,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,97; 28,72</t>
+          <t>16,54; 28,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 12,67</t>
+          <t>5,09; 12,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 24,99</t>
+          <t>12,57; 26,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,7; 33,97</t>
+          <t>21,75; 34,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,02; 29,31</t>
+          <t>17,33; 29,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 13,75</t>
+          <t>6,11; 13,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,84; 24,31</t>
+          <t>12,43; 24,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,45; 31,41</t>
+          <t>22,02; 31,13</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 26,86</t>
+          <t>17,92; 26,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,26; 11,6</t>
+          <t>6,21; 11,84</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 22,51</t>
+          <t>13,99; 22,83</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,16; 19,18</t>
+          <t>10,07; 18,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,66; 19,85</t>
+          <t>10,58; 19,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,55; 26,36</t>
+          <t>16,66; 26,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,18</t>
+          <t>5,87; 13,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,21; 28,08</t>
+          <t>17,04; 27,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,87; 18,24</t>
+          <t>9,78; 18,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,01; 23,35</t>
+          <t>14,05; 23,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 17,77</t>
+          <t>8,99; 18,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,86; 21,85</t>
+          <t>14,88; 21,71</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,55; 17,97</t>
+          <t>11,24; 17,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,49; 23,44</t>
+          <t>16,13; 23,24</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,12; 14,26</t>
+          <t>8,31; 14,58</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,11</t>
+          <t>17,17; 21,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,19; 25,42</t>
+          <t>20,5; 25,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,03; 22,98</t>
+          <t>18,26; 23,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,55; 17,93</t>
+          <t>12,61; 18,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,96; 24,96</t>
+          <t>19,83; 24,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,18; 25,27</t>
+          <t>20,22; 25,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,19; 22,11</t>
+          <t>17,47; 22,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,09; 19,64</t>
+          <t>14,87; 19,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,4; 22,84</t>
+          <t>19,32; 22,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,05; 24,67</t>
+          <t>21,02; 24,65</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,44; 21,8</t>
+          <t>18,33; 21,75</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,06</t>
+          <t>14,46; 18,2</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12730</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13786</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15476</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12091</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14766</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19376</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>17834</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14064</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>27496</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33162</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33310</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8506; 17991</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9158; 19934</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11300; 21580</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7439; 18190</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9926; 21041</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>13004; 25821</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12429; 24040</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8793; 21093</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20634; 35723</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>24991; 41306</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>26327; 41792</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18355; 34976</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>12107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27505</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28133</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13629</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>19228</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29742</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>28531</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>16330</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>31336</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>57246</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>56664</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>29959</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7589; 18355</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>20885; 35409</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>20965; 36147</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6544; 21956</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13347; 25637</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22385; 37804</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>21221; 36728</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>10688; 24335</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>23803; 40427</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>46953; 68468</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>46069; 67528</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19680; 41250</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>15534</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19798</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8864</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>13957</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18750</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20449</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8934</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>16422</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>34283</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40247</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>30379</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>10159; 22204</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14620; 26959</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5064; 14762</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9141; 19189</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13746; 25018</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13959; 27318</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5203; 14225</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>11448; 23151</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>26061; 42401</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>31292; 49416</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12003; 24129</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>23405; 38518</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>18913</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19050</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13268</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>19571</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>16768</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25083</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>14694</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>38484</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35819</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>48338</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>27963</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13641; 25481</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>12780; 25954</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>16504; 30399</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7839; 19699</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13686; 26891</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>10832; 23205</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18032; 32672</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7326; 24341</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>30557; 47876</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>27998; 44001</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>38976; 58444</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>18233; 39642</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12183</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10330</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3968</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6254</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>13749</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23702</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>20633</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>9324</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3959; 12292</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6994; 18234</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6106; 15197</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1651; 7159</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2821; 10679</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6879; 16341</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6216; 15463</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2755; 9640</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8410; 19863</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>16629; 31156</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>14703; 27894</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5541; 14229</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>11605</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16210</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11977</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9133</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>15629</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>10948</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>17055</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>21121</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>31839</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>22925</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>26188</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7146; 17140</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10768; 21848</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7763; 17708</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>5354; 13358</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>5752; 14865</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10320; 21721</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6161; 16731</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>11856; 22735</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>15184; 28437</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>23601; 39886</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>16073; 31142</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>19935; 33689</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>33058</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>30298</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>11154</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22291</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>37539</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>33605</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>13451</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>27726</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>70597</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>63903</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>24605</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>50017</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>25232; 41674</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>22941; 38862</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>6987; 17669</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>15652; 33447</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>29506; 46869</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>25256; 42277</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8763; 20023</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>19398; 37630</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>58189; 82263</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>50961; 75301</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>17426; 33238</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>39247; 64052</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>22144</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>24316</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>34697</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>11978</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>36214</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>23491</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>31036</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>19942</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>58358</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>47807</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>65733</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>31920</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>15897; 29747</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17423; 32040</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>27251; 43496</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>7720; 17865</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>27948; 45489</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>16629; 31048</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>23924; 40149</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>14096; 29138</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>47923; 69884</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>37613; 58702</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>53841; 77597</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>23980; 42061</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>133587</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>163145</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>143886</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>100314</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>131592</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>295424</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>333726</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>290005</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>231906</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>116961; 149439</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>145520; 180809</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>128350; 163278</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>83926; 120598</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>143277; 179505</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>151924; 189534</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>129406; 164987</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>113277; 149728</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>271234; 317509</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>307151; 360128</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>264740; 313988</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>206386; 259768</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP17-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 34,22</t>
+          <t>15,9; 33,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,95; 34,71</t>
+          <t>16,5; 34,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,7; 37,62</t>
+          <t>17,93; 36,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 24,82</t>
+          <t>9,92; 25,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 34,94</t>
+          <t>16,18; 34,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,07; 39,84</t>
+          <t>20,81; 39,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,46; 37,63</t>
+          <t>19,12; 37,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 26,58</t>
+          <t>11,11; 26,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,29; 31,67</t>
+          <t>19,04; 31,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,45; 33,79</t>
+          <t>20,97; 35,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 34,47</t>
+          <t>21,62; 34,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 22,91</t>
+          <t>12,49; 23,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 18,07</t>
+          <t>7,72; 17,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,95; 33,81</t>
+          <t>19,79; 33,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 35,01</t>
+          <t>20,61; 34,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 17,31</t>
+          <t>4,18; 16,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,27; 23,57</t>
+          <t>12,07; 24,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,14; 34,01</t>
+          <t>20,13; 33,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,24; 33,3</t>
+          <t>19,7; 33,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 19,07</t>
+          <t>7,86; 18,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,32; 19,22</t>
+          <t>11,33; 18,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21,75; 31,72</t>
+          <t>22,33; 31,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21,57; 31,62</t>
+          <t>22,11; 31,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,73; 16,21</t>
+          <t>7,66; 15,71</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,03; 32,85</t>
+          <t>15,22; 32,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,66; 39,94</t>
+          <t>20,95; 39,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 22,09</t>
+          <t>7,41; 21,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,69; 32,93</t>
+          <t>16,13; 32,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 35,57</t>
+          <t>18,76; 35,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,59; 38,34</t>
+          <t>21,17; 39,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 20,98</t>
+          <t>7,17; 21,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 34,47</t>
+          <t>16,05; 33,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,9; 30,74</t>
+          <t>18,71; 30,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 35,61</t>
+          <t>23,46; 36,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 17,92</t>
+          <t>8,82; 18,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,66; 30,71</t>
+          <t>19,06; 30,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 34,04</t>
+          <t>18,0; 33,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 33,71</t>
+          <t>17,17; 33,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,44; 39,5</t>
+          <t>22,33; 39,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 28,08</t>
+          <t>11,1; 28,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,3; 33,99</t>
+          <t>17,4; 33,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,33; 28,57</t>
+          <t>13,69; 28,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,21; 40,24</t>
+          <t>22,75; 39,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 31,15</t>
+          <t>8,74; 30,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,85; 31,09</t>
+          <t>19,32; 30,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 27,81</t>
+          <t>17,08; 27,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,65; 36,96</t>
+          <t>25,06; 37,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 26,73</t>
+          <t>12,81; 26,7</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 29,37</t>
+          <t>9,55; 29,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 41,53</t>
+          <t>16,92; 40,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,06; 34,98</t>
+          <t>13,99; 35,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 20,74</t>
+          <t>4,97; 20,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 23,81</t>
+          <t>6,32; 23,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,71; 34,95</t>
+          <t>15,42; 35,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,41; 33,36</t>
+          <t>12,92; 32,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 23,67</t>
+          <t>6,05; 22,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,7; 22,91</t>
+          <t>10,41; 22,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,34; 34,37</t>
+          <t>18,89; 34,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,38; 31,07</t>
+          <t>16,09; 30,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 18,91</t>
+          <t>7,32; 19,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,75; 30,58</t>
+          <t>13,16; 30,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,23; 39,02</t>
+          <t>20,02; 40,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,3; 32,63</t>
+          <t>13,69; 31,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,6; 28,93</t>
+          <t>12,05; 29,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,63; 24,89</t>
+          <t>9,32; 23,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,13; 36,05</t>
+          <t>17,43; 36,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,67; 28,98</t>
+          <t>10,75; 29,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,1; 40,46</t>
+          <t>21,24; 39,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,11; 24,56</t>
+          <t>12,72; 25,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20,31; 34,32</t>
+          <t>21,23; 35,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,35; 27,8</t>
+          <t>14,66; 27,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,48; 32,91</t>
+          <t>19,66; 33,63</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,62; 32,4</t>
+          <t>19,94; 31,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,54; 28,02</t>
+          <t>16,18; 28,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,86</t>
+          <t>4,84; 12,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,57; 26,86</t>
+          <t>12,66; 26,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,75; 34,55</t>
+          <t>22,17; 34,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,33; 29,01</t>
+          <t>17,38; 28,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 13,97</t>
+          <t>5,93; 13,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,43; 24,12</t>
+          <t>12,56; 24,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,02; 31,13</t>
+          <t>22,7; 31,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,92; 26,47</t>
+          <t>18,54; 26,89</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 11,84</t>
+          <t>6,18; 11,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 22,83</t>
+          <t>13,81; 22,49</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,07; 18,84</t>
+          <t>10,18; 18,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,58; 19,45</t>
+          <t>10,8; 19,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,66; 26,59</t>
+          <t>16,68; 26,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,87; 13,57</t>
+          <t>5,88; 13,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,04; 27,73</t>
+          <t>16,92; 27,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,78; 18,26</t>
+          <t>9,93; 18,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,05; 23,58</t>
+          <t>14,02; 23,33</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,99; 18,58</t>
+          <t>8,8; 18,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,88; 21,71</t>
+          <t>14,97; 21,54</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,24; 17,54</t>
+          <t>11,1; 17,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,13; 23,24</t>
+          <t>16,57; 23,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,31; 14,58</t>
+          <t>8,38; 14,53</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,17; 21,94</t>
+          <t>17,17; 22,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,5; 25,47</t>
+          <t>20,46; 25,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,22</t>
+          <t>18,16; 23,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,61; 18,13</t>
+          <t>12,34; 17,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,83; 24,84</t>
+          <t>19,86; 24,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,22; 25,23</t>
+          <t>20,17; 25,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,47; 22,27</t>
+          <t>17,53; 22,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,65</t>
+          <t>14,87; 19,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,32; 22,62</t>
+          <t>19,4; 22,85</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,02; 24,65</t>
+          <t>21,06; 24,76</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,33; 21,75</t>
+          <t>18,47; 21,93</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,46; 18,2</t>
+          <t>14,56; 18,08</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8506; 17991</t>
+          <t>8356; 17435</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9158; 19934</t>
+          <t>9477; 20031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11300; 21580</t>
+          <t>10288; 21195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7439; 18190</t>
+          <t>7271; 18823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9926; 21041</t>
+          <t>9743; 20804</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13004; 25821</t>
+          <t>13487; 25753</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12429; 24040</t>
+          <t>12215; 23945</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8793; 21093</t>
+          <t>8816; 20912</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20634; 35723</t>
+          <t>21469; 35101</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24991; 41306</t>
+          <t>25627; 43033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26327; 41792</t>
+          <t>26209; 41956</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18355; 34976</t>
+          <t>19058; 35470</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7589; 18355</t>
+          <t>7843; 18028</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20885; 35409</t>
+          <t>20727; 35115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20965; 36147</t>
+          <t>21277; 35714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6544; 21956</t>
+          <t>5304; 21213</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13347; 25637</t>
+          <t>13127; 26343</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22385; 37804</t>
+          <t>22378; 37605</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21221; 36728</t>
+          <t>21731; 36585</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10688; 24335</t>
+          <t>10033; 24206</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23803; 40427</t>
+          <t>23827; 39738</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46953; 68468</t>
+          <t>48196; 68562</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46069; 67528</t>
+          <t>47219; 66787</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19680; 41250</t>
+          <t>19487; 39975</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10159; 22204</t>
+          <t>10289; 22042</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14620; 26959</t>
+          <t>14139; 26573</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5064; 14762</t>
+          <t>4952; 14465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9141; 19189</t>
+          <t>9398; 19035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13746; 25018</t>
+          <t>13190; 24893</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13959; 27318</t>
+          <t>15081; 28182</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5203; 14225</t>
+          <t>4863; 14533</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11448; 23151</t>
+          <t>10779; 22526</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26061; 42401</t>
+          <t>25805; 41779</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31292; 49416</t>
+          <t>32551; 49965</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12003; 24129</t>
+          <t>11869; 24607</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23405; 38518</t>
+          <t>23912; 38839</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13641; 25481</t>
+          <t>13475; 25424</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12780; 25954</t>
+          <t>13223; 25742</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16504; 30399</t>
+          <t>17187; 30452</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7839; 19699</t>
+          <t>7785; 19779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13686; 26891</t>
+          <t>13769; 26503</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10832; 23205</t>
+          <t>11120; 23319</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18032; 32672</t>
+          <t>18470; 32280</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7326; 24341</t>
+          <t>6829; 23791</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30557; 47876</t>
+          <t>29743; 46661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27998; 44001</t>
+          <t>27024; 43882</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38976; 58444</t>
+          <t>39630; 58820</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18233; 39642</t>
+          <t>18997; 39587</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3959; 12292</t>
+          <t>3995; 12536</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6994; 18234</t>
+          <t>7427; 17738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6106; 15197</t>
+          <t>6078; 15342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1651; 7159</t>
+          <t>1714; 7147</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2821; 10679</t>
+          <t>2834; 10450</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6879; 16341</t>
+          <t>7208; 16659</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6216; 15463</t>
+          <t>5988; 15207</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2755; 9640</t>
+          <t>2462; 9313</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8410; 19863</t>
+          <t>9027; 19547</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16629; 31156</t>
+          <t>17123; 31314</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14703; 27894</t>
+          <t>14445; 27681</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5541; 14229</t>
+          <t>5508; 14579</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7146; 17140</t>
+          <t>7377; 16884</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10768; 21848</t>
+          <t>11209; 22525</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7763; 17708</t>
+          <t>7431; 17356</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5354; 13358</t>
+          <t>5564; 13809</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5752; 14865</t>
+          <t>5566; 14096</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10320; 21721</t>
+          <t>10501; 21999</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6161; 16731</t>
+          <t>6205; 17039</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11856; 22735</t>
+          <t>11935; 22287</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15184; 28437</t>
+          <t>14729; 29182</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23601; 39886</t>
+          <t>24674; 41241</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16073; 31142</t>
+          <t>16416; 30549</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19935; 33689</t>
+          <t>20124; 34420</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25232; 41674</t>
+          <t>25652; 41071</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22941; 38862</t>
+          <t>22440; 38979</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6987; 17669</t>
+          <t>6643; 16960</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15652; 33447</t>
+          <t>15767; 32374</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29506; 46869</t>
+          <t>30077; 46282</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25256; 42277</t>
+          <t>25332; 42158</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8763; 20023</t>
+          <t>8499; 19681</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19398; 37630</t>
+          <t>19590; 38867</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>58189; 82263</t>
+          <t>59993; 83340</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50961; 75301</t>
+          <t>52730; 76502</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17426; 33238</t>
+          <t>17341; 32388</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>39247; 64052</t>
+          <t>38726; 63081</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15897; 29747</t>
+          <t>16078; 29821</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17423; 32040</t>
+          <t>17793; 32088</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27251; 43496</t>
+          <t>27288; 43344</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7720; 17865</t>
+          <t>7744; 17913</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27948; 45489</t>
+          <t>27751; 44950</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16629; 31048</t>
+          <t>16885; 32010</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23924; 40149</t>
+          <t>23877; 39718</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>14096; 29138</t>
+          <t>13799; 28375</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>47923; 69884</t>
+          <t>48189; 69337</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37613; 58702</t>
+          <t>37161; 58693</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53841; 77597</t>
+          <t>55323; 77151</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>23980; 42061</t>
+          <t>24164; 41905</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>116961; 149439</t>
+          <t>116903; 151293</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>145520; 180809</t>
+          <t>145285; 183629</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>128350; 163278</t>
+          <t>127645; 161928</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>83926; 120598</t>
+          <t>82080; 116826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>143277; 179505</t>
+          <t>143533; 179665</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>151924; 189534</t>
+          <t>151532; 188742</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>129406; 164987</t>
+          <t>129843; 164378</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>113277; 149728</t>
+          <t>113296; 151520</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>271234; 317509</t>
+          <t>272281; 320747</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>307151; 360128</t>
+          <t>307721; 361743</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>264740; 313988</t>
+          <t>266751; 316631</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>206386; 259768</t>
+          <t>207822; 258123</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP17-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP17-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24,52%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27,92%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18,99%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>24,22%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>26,97%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,52%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>27,92%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,9; 33,17</t>
+          <t>16,04; 34,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,5; 34,88</t>
+          <t>20,9; 40,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 36,94</t>
+          <t>18,45; 38,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,92; 25,69</t>
+          <t>11,98; 28,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,18; 34,55</t>
+          <t>16,59; 34,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,81; 39,74</t>
+          <t>15,53; 34,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,12; 37,49</t>
+          <t>18,21; 37,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,11; 26,35</t>
+          <t>12,36; 29,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 31,12</t>
+          <t>18,87; 31,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,97; 35,2</t>
+          <t>20,63; 34,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21,62; 34,6</t>
+          <t>20,39; 34,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 23,24</t>
+          <t>14,21; 25,75</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17,68%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>26,76%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25,87%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,92%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>26,27%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>27,25%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>26,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>25,87%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 17,75</t>
+          <t>12,09; 23,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,79; 33,53</t>
+          <t>19,74; 33,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,61; 34,59</t>
+          <t>19,65; 32,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,18; 16,72</t>
+          <t>8,16; 18,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,07; 24,22</t>
+          <t>7,2; 17,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 33,83</t>
+          <t>19,76; 33,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,7; 33,17</t>
+          <t>19,85; 33,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 18,97</t>
+          <t>8,59; 20,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 18,89</t>
+          <t>11,32; 19,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 31,76</t>
+          <t>21,7; 31,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,11; 31,28</t>
+          <t>22,04; 31,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,71</t>
+          <t>9,39; 17,93</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26,66%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28,7%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23,65%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>29,33%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13,26%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>23,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 32,61</t>
+          <t>19,48; 35,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,95; 39,37</t>
+          <t>21,06; 38,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 21,64</t>
+          <t>7,9; 20,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,13; 32,67</t>
+          <t>15,51; 32,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,76; 35,4</t>
+          <t>15,35; 32,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 39,55</t>
+          <t>20,97; 39,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 21,43</t>
+          <t>6,94; 21,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,05; 33,54</t>
+          <t>16,28; 33,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 30,29</t>
+          <t>19,43; 31,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23,46; 36,01</t>
+          <t>22,67; 35,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,28</t>
+          <t>9,05; 18,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,06; 30,96</t>
+          <t>18,18; 29,52</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20,64%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19,31%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>25,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>24,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30,22%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18,92%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,9%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,0; 33,96</t>
+          <t>17,31; 33,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 33,43</t>
+          <t>13,88; 28,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,33; 39,57</t>
+          <t>22,74; 40,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,1; 28,2</t>
+          <t>9,91; 32,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,4; 33,5</t>
+          <t>17,95; 34,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 28,71</t>
+          <t>17,58; 33,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 39,76</t>
+          <t>22,52; 39,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,74; 30,45</t>
+          <t>11,22; 29,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,32; 30,3</t>
+          <t>19,08; 31,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,08; 27,73</t>
+          <t>17,45; 28,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,06; 37,19</t>
+          <t>24,21; 36,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 26,7</t>
+          <t>13,27; 26,42</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,95%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24,64%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22,23%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>17,91%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>27,75%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>23,78%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>24,64%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,55; 29,95</t>
+          <t>6,23; 23,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,92; 40,41</t>
+          <t>15,83; 37,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,99; 35,32</t>
+          <t>12,74; 32,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,97; 20,71</t>
+          <t>6,74; 24,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,32; 23,3</t>
+          <t>9,68; 29,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,42; 35,63</t>
+          <t>16,94; 39,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,92; 32,81</t>
+          <t>13,62; 35,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 22,87</t>
+          <t>5,12; 22,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,41; 22,55</t>
+          <t>10,22; 23,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18,89; 34,54</t>
+          <t>18,75; 35,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,09; 30,83</t>
+          <t>15,8; 30,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 19,38</t>
+          <t>7,78; 20,08</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18,96%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>29,6%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>20,7%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>28,95%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>22,07%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18,96%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,16; 30,12</t>
+          <t>9,75; 25,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,02; 40,23</t>
+          <t>17,46; 35,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,69; 31,98</t>
+          <t>10,83; 29,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,05; 29,91</t>
+          <t>20,99; 41,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 23,6</t>
+          <t>13,34; 30,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,43; 36,52</t>
+          <t>20,11; 40,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,75; 29,51</t>
+          <t>13,31; 32,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,24; 39,67</t>
+          <t>12,18; 28,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,72; 25,2</t>
+          <t>13,14; 24,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21,23; 35,48</t>
+          <t>20,7; 34,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14,66; 27,27</t>
+          <t>14,45; 27,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,66; 33,63</t>
+          <t>18,45; 31,62</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19,7%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>25,7%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>21,84%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>8,12%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,9%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,94; 31,93</t>
+          <t>21,7; 33,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,18; 28,1</t>
+          <t>18,02; 29,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,84; 12,35</t>
+          <t>6,03; 13,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,66; 26,0</t>
+          <t>14,21; 26,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,17; 34,12</t>
+          <t>19,97; 32,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,38; 28,93</t>
+          <t>16,97; 28,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 13,73</t>
+          <t>5,06; 12,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,56; 24,91</t>
+          <t>11,44; 21,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,7; 31,54</t>
+          <t>22,45; 31,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,54; 26,89</t>
+          <t>18,29; 26,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,54</t>
+          <t>6,26; 11,6</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,81; 22,49</t>
+          <t>14,22; 22,26</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22,07%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>14,02%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>14,76%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>21,21%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,18; 18,89</t>
+          <t>17,21; 28,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 19,48</t>
+          <t>9,87; 18,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,68; 26,5</t>
+          <t>14,01; 23,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 13,61</t>
+          <t>8,23; 17,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,92; 27,4</t>
+          <t>10,16; 19,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,93; 18,83</t>
+          <t>10,66; 19,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,02; 23,33</t>
+          <t>16,55; 26,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,1</t>
+          <t>5,09; 12,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,97; 21,54</t>
+          <t>14,86; 21,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11,1; 17,53</t>
+          <t>11,55; 17,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,57; 23,11</t>
+          <t>16,49; 23,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 14,53</t>
+          <t>7,43; 13,28</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>22,39%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>19,62%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>22,98%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>20,47%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,22</t>
+          <t>19,96; 24,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,46; 25,86</t>
+          <t>20,18; 25,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,16; 23,03</t>
+          <t>17,19; 22,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,34; 17,56</t>
+          <t>15,03; 19,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,86</t>
+          <t>17,38; 22,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,17; 25,13</t>
+          <t>20,19; 25,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,53; 22,19</t>
+          <t>18,03; 22,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14,87; 19,89</t>
+          <t>13,0; 17,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19,4; 22,85</t>
+          <t>19,4; 22,84</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21,06; 24,76</t>
+          <t>21,05; 24,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18,47; 21,93</t>
+          <t>18,44; 21,8</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,56; 18,08</t>
+          <t>14,73; 18,15</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2078,37 +2078,37 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14766</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19376</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17834</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12180</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12730</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>13786</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>15476</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12091</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14766</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19376</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17834</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14064</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>23292</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8356; 17435</t>
+          <t>9662; 20769</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9477; 20031</t>
+          <t>13543; 26512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10288; 21195</t>
+          <t>11784; 24342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7271; 18823</t>
+          <t>7684; 18347</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9743; 20804</t>
+          <t>8719; 18056</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13487; 25753</t>
+          <t>8916; 19996</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12215; 23945</t>
+          <t>10446; 21339</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8816; 20912</t>
+          <t>6984; 16469</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21469; 35101</t>
+          <t>21281; 35279</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25627; 43033</t>
+          <t>25212; 42435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26209; 41956</t>
+          <t>24720; 41684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19058; 35470</t>
+          <t>17136; 31059</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>19228</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29742</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28531</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>14419</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>12107</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>27505</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28133</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13629</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19228</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29742</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28531</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16330</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>29959</t>
+          <t>27532</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7843; 18028</t>
+          <t>13150; 25816</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20727; 35115</t>
+          <t>21941; 37164</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21277; 35714</t>
+          <t>21674; 36136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5304; 21213</t>
+          <t>9452; 21024</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13127; 26343</t>
+          <t>7312; 18079</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22378; 37605</t>
+          <t>20692; 35448</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21731; 36585</t>
+          <t>20493; 35096</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10033; 24206</t>
+          <t>8640; 20274</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23827; 39738</t>
+          <t>23798; 40372</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48196; 68562</t>
+          <t>46836; 68219</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>47219; 66787</t>
+          <t>47056; 67970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19487; 39975</t>
+          <t>20315; 38791</t>
         </is>
       </c>
     </row>
@@ -2489,32 +2489,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18750</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20449</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8934</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>14042</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>15534</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>19798</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>8864</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13957</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18750</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20449</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8934</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16422</t>
+          <t>13571</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30379</t>
+          <t>27613</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10289; 22042</t>
+          <t>13698; 24970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14139; 26573</t>
+          <t>15008; 27288</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4952; 14465</t>
+          <t>5357; 14225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9398; 19035</t>
+          <t>9207; 19504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13190; 24893</t>
+          <t>10377; 21977</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15081; 28182</t>
+          <t>14153; 26375</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4863; 14533</t>
+          <t>4640; 14628</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10779; 22526</t>
+          <t>9209; 18961</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25805; 41779</t>
+          <t>26803; 43078</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32551; 49965</t>
+          <t>31463; 49551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11869; 24607</t>
+          <t>12189; 25399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23912; 38839</t>
+          <t>21080; 34222</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19571</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16768</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25083</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>13934</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>18913</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>19050</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>23256</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13268</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19571</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16768</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25083</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27963</t>
+          <t>27165</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13475; 25424</t>
+          <t>13691; 26116</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13223; 25742</t>
+          <t>11276; 23314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17187; 30452</t>
+          <t>18457; 32470</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7785; 19779</t>
+          <t>7152; 23740</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13769; 26503</t>
+          <t>13439; 25856</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11120; 23319</t>
+          <t>13538; 25960</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18470; 32280</t>
+          <t>17334; 30459</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6829; 23791</t>
+          <t>7948; 21205</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29743; 46661</t>
+          <t>29380; 47918</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27024; 43882</t>
+          <t>27617; 45133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39630; 58820</t>
+          <t>38288; 57904</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18997; 39587</t>
+          <t>18971; 37778</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6254</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11520</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10302</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5368</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7495</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>12183</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>10330</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6254</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11520</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>10302</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9604</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3995; 12536</t>
+          <t>2796; 10452</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7427; 17738</t>
+          <t>7400; 17321</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6078; 15342</t>
+          <t>5903; 15172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1714; 7147</t>
+          <t>2669; 9758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2834; 10450</t>
+          <t>4051; 12158</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7208; 16659</t>
+          <t>7438; 17498</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5988; 15207</t>
+          <t>5915; 15539</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2462; 9313</t>
+          <t>1824; 7967</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9027; 19547</t>
+          <t>8864; 20170</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17123; 31314</t>
+          <t>16998; 31831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14445; 27681</t>
+          <t>14190; 27596</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5508; 14579</t>
+          <t>5846; 15098</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>9516</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15629</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10948</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14485</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>11605</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>16210</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>11977</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9133</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9516</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>15629</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>10948</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>23501</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7377; 16884</t>
+          <t>5824; 14932</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11209; 22525</t>
+          <t>10521; 21620</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7431; 17356</t>
+          <t>6254; 17124</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5564; 13809</t>
+          <t>10271; 20287</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5566; 14096</t>
+          <t>7477; 16919</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10501; 21999</t>
+          <t>11261; 22750</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6205; 17039</t>
+          <t>7224; 17531</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11935; 22287</t>
+          <t>5573; 13209</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14729; 29182</t>
+          <t>15218; 28722</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24674; 41241</t>
+          <t>24058; 40400</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16416; 30549</t>
+          <t>16186; 30501</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20124; 34420</t>
+          <t>17474; 29942</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>37539</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>33605</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13451</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>27852</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>33058</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>30298</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>11154</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>22291</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>37539</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>33605</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13451</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27726</t>
+          <t>19843</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>47695</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25652; 41071</t>
+          <t>29434; 46079</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>22440; 38979</t>
+          <t>26267; 42723</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6643; 16960</t>
+          <t>8651; 19712</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15767; 32374</t>
+          <t>20083; 36992</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30077; 46282</t>
+          <t>25684; 41722</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25332; 42158</t>
+          <t>23536; 39841</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8499; 19681</t>
+          <t>6953; 17400</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>19590; 38867</t>
+          <t>14020; 26933</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>59993; 83340</t>
+          <t>59324; 83007</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52730; 76502</t>
+          <t>52040; 76392</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17341; 32388</t>
+          <t>17586; 32574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>38726; 63081</t>
+          <t>37539; 58739</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>36214</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>23491</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>31036</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19441</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>22144</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>24316</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>34697</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>11978</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>36214</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>23491</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>31036</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31920</t>
+          <t>30831</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>16078; 29821</t>
+          <t>28233; 46061</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17793; 32088</t>
+          <t>16783; 31005</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27288; 43344</t>
+          <t>23858; 39752</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7744; 17913</t>
+          <t>13121; 27426</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27751; 44950</t>
+          <t>16041; 30287</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16885; 32010</t>
+          <t>17556; 32698</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23877; 39718</t>
+          <t>27069; 43123</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>13799; 28375</t>
+          <t>7152; 17037</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>48189; 69337</t>
+          <t>47845; 70346</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37161; 58693</t>
+          <t>38662; 60163</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55323; 77151</t>
+          <t>55039; 78235</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>24164; 41905</t>
+          <t>22298; 39836</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>161836</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>170581</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>146119</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>121722</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>133587</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>163145</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>143886</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>100314</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>161836</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>170581</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>146119</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>95512</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>231906</t>
+          <t>217234</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>116903; 151293</t>
+          <t>144249; 180387</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>145285; 183629</t>
+          <t>151559; 189799</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>127645; 161928</t>
+          <t>127328; 163833</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82080; 116826</t>
+          <t>105312; 138293</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>143533; 179665</t>
+          <t>118374; 150599</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>151532; 188742</t>
+          <t>143342; 180478</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>129843; 164378</t>
+          <t>126750; 161597</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>113296; 151520</t>
+          <t>81764; 111378</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>272281; 320747</t>
+          <t>272305; 320612</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>307721; 361743</t>
+          <t>307512; 360492</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>266751; 316631</t>
+          <t>266309; 314781</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>207822; 258123</t>
+          <t>195795; 241364</t>
         </is>
       </c>
     </row>
